--- a/Inam_Restaurant_TestCases.xlsx
+++ b/Inam_Restaurant_TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Testing Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1787A6-99D2-4826-9C86-1389AADC1987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88492746-AF2F-4EE5-9CDD-75228B381982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="295">
   <si>
     <t>Inam Restaurant Website — Test Case Sheet</t>
+  </si>
+  <si>
+    <t>URL: https://inam0980.pythonanywhere.com/   |   Tester: Inam Khan   |   Date: 21/05/2026_</t>
   </si>
   <si>
     <t>TC ID</t>
@@ -268,10 +271,10 @@
 4. Click Submit</t>
   </si>
   <si>
-    <t>Valid username &amp; password</t>
-  </si>
-  <si>
     <t>User logs in and is redirected to dashboard / home</t>
+  </si>
+  <si>
+    <t>Automated using Selenium (Python). Screenshot evidence available.</t>
   </si>
   <si>
     <t>FUN-011</t>
@@ -285,9 +288,6 @@
 3. Click Submit</t>
   </si>
   <si>
-    <t>Valid user, wrong password</t>
-  </si>
-  <si>
     <t>Error message shown: 'Invalid credentials' (no login)</t>
   </si>
   <si>
@@ -319,9 +319,6 @@
     <t>1. Enter random username
 2. Enter random password
 3. Click Submit</t>
-  </si>
-  <si>
-    <t>abcxyz123 / pass123</t>
   </si>
   <si>
     <t>Error message: user not found / invalid credentials</t>
@@ -753,11 +750,6 @@
     <t>Login page open</t>
   </si>
   <si>
-    <t>1. Username: admin' OR '1'='1
-2. Password: anything
-3. Submit</t>
-  </si>
-  <si>
     <t>admin' OR '1'='1</t>
   </si>
   <si>
@@ -975,14 +967,25 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>URL: https://inam0980.pythonanywhere.com/   |   Tester: Inam Khan   |   Date: 21/05/2026_</t>
+    <t>username=inam0980 &amp; password=inam0980</t>
+  </si>
+  <si>
+    <t>Valid user=inam0980, wrong password=1234</t>
+  </si>
+  <si>
+    <t>khan123 / inamkhan234</t>
+  </si>
+  <si>
+    <t>1. Username: admin' 
+2. Password: khan123
+3. Submit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1037,8 +1040,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1075,8 +1084,13 @@
         <fgColor rgb="FFC00000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1099,11 +1113,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1140,6 +1169,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1468,482 +1500,486 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
+      <c r="A2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
     </row>
     <row r="3" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:12" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="F7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="4"/>
+    </row>
+    <row r="9" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>73</v>
+        <v>291</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>74</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="14" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>79</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>81</v>
@@ -1961,25 +1997,27 @@
         <v>85</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>87</v>
@@ -1991,1181 +2029,1185 @@
         <v>88</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="I17" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="G18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="I18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="4"/>
+    </row>
+    <row r="19" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="4"/>
-    </row>
-    <row r="19" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="4" t="s">
+    </row>
+    <row r="20" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="1:12" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H21" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="J21" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="K21" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="L21" s="4"/>
+    </row>
+    <row r="22" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="22" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="I22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="I23" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="I24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L24" s="4"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="I25" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="4" t="s">
+      <c r="I27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="4" t="s">
+      <c r="G29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="4" t="s">
+      <c r="I29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="4"/>
-    </row>
-    <row r="30" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="4" t="s">
+      <c r="I30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="4"/>
+    </row>
+    <row r="31" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="4"/>
-    </row>
-    <row r="31" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="D31" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="F31" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="I31" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="J31" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="4"/>
+    </row>
+    <row r="32" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="J31" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="4"/>
-    </row>
-    <row r="32" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="E32" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="4"/>
+    </row>
+    <row r="33" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="D33" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L32" s="4"/>
-    </row>
-    <row r="33" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="I34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" s="4"/>
+    </row>
+    <row r="35" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L33" s="4"/>
-    </row>
-    <row r="34" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L34" s="4"/>
-    </row>
-    <row r="35" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="4"/>
-    </row>
-    <row r="36" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="G36" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="H36" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="I36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="4"/>
+    </row>
+    <row r="37" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L36" s="4"/>
-    </row>
-    <row r="37" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H37" s="4" t="s">
+      <c r="I37" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="J37" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="J37" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L37" s="4"/>
-    </row>
-    <row r="38" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="D38" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="G38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H38" s="4" t="s">
+      <c r="I38" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="4"/>
+    </row>
+    <row r="39" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="4"/>
-    </row>
-    <row r="39" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
+      <c r="B39" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="F39" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="I39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="H39" s="4" t="s">
+    </row>
+    <row r="40" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="4" t="s">
+      <c r="B40" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
+      <c r="E40" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="F40" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="G40" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="H40" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="I40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="4"/>
+    </row>
+    <row r="41" spans="1:12" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="4"/>
-    </row>
-    <row r="41" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
+      <c r="C41" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="E41" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="F41" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="G41" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="I41" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="J41" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="4"/>
+    </row>
+    <row r="42" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="J41" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L41" s="4"/>
-    </row>
-    <row r="42" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
+      <c r="C42" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="E42" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="F42" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="H42" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="I42" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H42" s="4" t="s">
+    </row>
+    <row r="43" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
+      <c r="C43" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="E43" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="G43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="I43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H43" s="4" t="s">
+    </row>
+    <row r="44" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
+      <c r="C44" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="E44" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="F44" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="I44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="4"/>
+    </row>
+    <row r="45" spans="1:12" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44" s="4"/>
-    </row>
-    <row r="45" spans="1:12" ht="58" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
+      <c r="C45" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="E45" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="F45" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="G45" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H45" s="4" t="s">
+      <c r="J45" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="4"/>
+    </row>
+    <row r="46" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="J45" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L45" s="4"/>
-    </row>
-    <row r="46" spans="1:12" ht="29" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
+      <c r="C46" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="E46" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="F46" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="G46" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="H46" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="I46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" s="4"/>
+    </row>
+    <row r="47" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L46" s="4"/>
-    </row>
-    <row r="47" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
+      <c r="C47" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="E47" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="F47" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="G47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="I47" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="4"/>
+    </row>
+    <row r="48" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H47" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="4"/>
-    </row>
-    <row r="48" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
+      <c r="C48" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="E48" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="F48" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="G48" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>287</v>
-      </c>
       <c r="I48" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L48" s="4"/>
     </row>
@@ -3189,30 +3231,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
+      <c r="A1" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2">
         <f>COUNTIF('Test Cases'!C:C,"Functional")</f>
@@ -3229,7 +3271,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B4" s="2">
         <f>COUNTIF('Test Cases'!C:C,"UI/UX")</f>
@@ -3246,7 +3288,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B5" s="2">
         <f>COUNTIF('Test Cases'!C:C,"Performance")</f>
@@ -3263,7 +3305,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('Test Cases'!C:C,"Security")</f>
@@ -3280,7 +3322,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B7" s="12">
         <f>SUM(B3:B6)</f>
